--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,471 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129013194</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56613</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västernäs, Östernäs och Uppnäs 3, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>723645</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6626275</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129013099</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56603</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västernäs, Östernäs och Uppnäs 3, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>723645</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6626275</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129013129</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56608</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västernäs, Östernäs och Uppnäs 3, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>723645</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6626275</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129013187</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56606</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100111</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pipistrellus nathusii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västernäs, Östernäs och Uppnäs 3, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>723645</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626275</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013092</v>
       </c>
       <c r="B2" t="n">
-        <v>56589</v>
+        <v>56591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129013194</v>
       </c>
       <c r="B3" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>129013099</v>
       </c>
       <c r="B4" t="n">
-        <v>56603</v>
+        <v>56605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129013129</v>
       </c>
       <c r="B5" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>129013187</v>
       </c>
       <c r="B6" t="n">
-        <v>56606</v>
+        <v>56608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129013092</v>
       </c>
       <c r="B2" t="n">
-        <v>56591</v>
+        <v>56593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129013194</v>
       </c>
       <c r="B3" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>129013099</v>
       </c>
       <c r="B4" t="n">
-        <v>56605</v>
+        <v>56607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129013129</v>
       </c>
       <c r="B5" t="n">
-        <v>56610</v>
+        <v>56612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>129013187</v>
       </c>
       <c r="B6" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129013194</v>
       </c>
       <c r="B3" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>129013099</v>
       </c>
       <c r="B4" t="n">
-        <v>56607</v>
+        <v>56610</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129013129</v>
       </c>
       <c r="B5" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>129013187</v>
       </c>
       <c r="B6" t="n">
-        <v>56610</v>
+        <v>56613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129013194</v>
       </c>
       <c r="B3" t="n">
-        <v>56620</v>
+        <v>56715</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129013194</v>
       </c>
       <c r="B3" t="n">
-        <v>56715</v>
+        <v>56741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129013194</v>
       </c>
       <c r="B3" t="n">
-        <v>56741</v>
+        <v>56743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129013194</v>
       </c>
       <c r="B3" t="n">
-        <v>56743</v>
+        <v>56751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>129013194</v>
       </c>
       <c r="B3" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129013092</v>
+        <v>129013099</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129013194</v>
+        <v>129013187</v>
       </c>
       <c r="B3" t="n">
-        <v>56772</v>
+        <v>56833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206000</v>
+        <v>100111</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -888,16 +888,7 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Åsa Duell</t>
@@ -912,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129013099</v>
+        <v>129013722</v>
       </c>
       <c r="B4" t="n">
-        <v>56610</v>
+        <v>56833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,26 +914,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -960,14 +951,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västernäs, Östernäs och Uppnäs 3, Upl</t>
+          <t>Västernäs, Östernäs och Uppnäs 4, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723645</v>
+        <v>723554</v>
       </c>
       <c r="R4" t="n">
-        <v>6626275</v>
+        <v>6626187</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,6 +991,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sociala läten på 415 av inspelningarna</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1025,7 @@
         <v>129013129</v>
       </c>
       <c r="B5" t="n">
-        <v>56615</v>
+        <v>56835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129013187</v>
+        <v>129013370</v>
       </c>
       <c r="B6" t="n">
-        <v>56613</v>
+        <v>56835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,26 +1147,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1188,14 +1184,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västernäs, Östernäs och Uppnäs 3, Upl</t>
+          <t>Västernäs, Östernäs och Uppnäs 4, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723645</v>
+        <v>723554</v>
       </c>
       <c r="R6" t="n">
-        <v>6626275</v>
+        <v>6626187</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,6 +1247,561 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129013092</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västernäs, Östernäs och Uppnäs 3, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>723645</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6626275</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129013215</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västernäs, Östernäs och Uppnäs 4, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>723554</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6626187</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129013194</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västernäs, Östernäs och Uppnäs 3, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>723645</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6626275</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129971381</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106155</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västernäs, Östernäs och Uppnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>723648</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6626035</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Viktor Bolin</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist, Viktor Bolin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129971374</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västernäs, Östernäs och Uppnäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>723805</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6626243</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rådmansö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist, Viktor Bolin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3444-2023 artfynd.xlsx
+++ b/artfynd/A 3444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129013099</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129013187</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129013722</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129013129</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129013370</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129013092</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129013215</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129013194</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1700,6 +1745,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971381</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1802,8 +1852,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971374</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>